--- a/docs/testing/test-case-report.xlsx
+++ b/docs/testing/test-case-report.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kisune_Alvarez\Desktop\MyProjects\AI-IT-Job-Market-Consultant\docs\testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4F2874-DBCA-45D9-A65F-A94AEC04AE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9A312E-092B-4BF1-82A0-04E8C90A5AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="821" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="821" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cover" sheetId="97" r:id="rId1"/>
+    <sheet name="Cover Page" sheetId="97" r:id="rId1"/>
     <sheet name="Test User Module" sheetId="122" r:id="rId2"/>
     <sheet name="Test Temp Module" sheetId="123" r:id="rId3"/>
     <sheet name="System Test " sheetId="125" r:id="rId4"/>
-    <sheet name="Test case report" sheetId="107" r:id="rId5"/>
+    <sheet name="Conclusion Report" sheetId="107" r:id="rId5"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId6"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>Fail</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Postman và Selenium</t>
   </si>
   <si>
     <t>TEST COVER</t>
@@ -216,6 +213,30 @@
   <si>
     <t>Revision History:</t>
   </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>Automated GitHub Issues integration</t>
+  </si>
+  <si>
+    <t>Postman and Selenium</t>
+  </si>
+  <si>
+    <t>Mock</t>
+  </si>
+  <si>
+    <t>Mock Testing</t>
+  </si>
+  <si>
+    <t>This is a test mock</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
 </sst>
 </file>
 
@@ -225,7 +246,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -713,7 +734,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1010,18 +1031,39 @@
     <xf numFmtId="1" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1031,6 +1073,72 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="10"/>
     </xf>
@@ -1049,15 +1157,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1067,95 +1166,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1548,7 +1575,7 @@
     <row r="2" spans="1:9" ht="21" thickBot="1">
       <c r="A2" s="6"/>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1559,39 +1586,39 @@
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="6"/>
       <c r="B3" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="112" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
+        <v>16</v>
+      </c>
+      <c r="C3" s="114" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" s="6"/>
       <c r="B4" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="158">
+        <v>15</v>
+      </c>
+      <c r="C4" s="116">
         <v>46221</v>
       </c>
-      <c r="D4" s="158"/>
-      <c r="E4" s="159"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="117"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="114" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="115"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
@@ -1604,61 +1631,73 @@
     <row r="7" spans="1:9" ht="15.75" thickBot="1">
       <c r="A7" s="6"/>
       <c r="B7" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="B8" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="E8" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="39" t="s">
+      <c r="H8" s="48" t="s">
         <v>25</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1" ht="21" customHeight="1">
       <c r="B9" s="96">
-        <v>46095</v>
+        <v>46217</v>
       </c>
       <c r="C9" s="90" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="97"/>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" ht="21" customHeight="1">
-      <c r="B10" s="96"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="92"/>
+      <c r="B10" s="96">
+        <v>46249</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>19</v>
+      </c>
       <c r="H10" s="97"/>
     </row>
     <row r="11" spans="1:9" s="7" customFormat="1" ht="21" customHeight="1">
@@ -1834,100 +1873,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="142"/>
+      <c r="B1" s="140"/>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
     </row>
     <row r="2" spans="1:15" s="62" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
       <c r="E2" s="61"/>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
     </row>
     <row r="3" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="138"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
       <c r="O3" s="66"/>
     </row>
     <row r="4" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="139" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="141"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="139"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
       <c r="O4" s="66"/>
     </row>
     <row r="5" spans="1:15" s="70" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="139" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="141"/>
+        <v>30</v>
+      </c>
+      <c r="B5" s="137" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="139"/>
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
       <c r="O5" s="69"/>
     </row>
     <row r="6" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -1936,14 +1975,14 @@
       </c>
       <c r="B6" s="104">
         <f>COUNTIFS(J12:J200, "Pass", A12:A200, "&lt;&gt;*AI")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="105" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="104">
         <f>COUNTIF(L13:L200,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="106" t="s">
         <v>3</v>
@@ -1954,12 +1993,12 @@
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
       <c r="O6" s="66"/>
     </row>
     <row r="7" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -1978,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="111">
         <f>COUNTIF(A12:A200, "TC*")</f>
@@ -1986,19 +2025,19 @@
       </c>
       <c r="G7" s="72"/>
       <c r="H7" s="72"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
       <c r="O7" s="66"/>
     </row>
     <row r="8" spans="1:15" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="144"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
       <c r="E8" s="71"/>
       <c r="F8" s="71"/>
       <c r="G8" s="71"/>
@@ -2012,130 +2051,152 @@
       <c r="O8" s="66"/>
     </row>
     <row r="9" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="145" t="s">
+      <c r="A9" s="129" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="145" t="s">
+      <c r="C9" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="D9" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145" t="s">
+      <c r="I9" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="145" t="s">
+      <c r="J9" s="129" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="145" t="s">
+      <c r="L9" s="129" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="130" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="145" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="152" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="145" t="s">
-        <v>40</v>
-      </c>
       <c r="O9" s="66"/>
     </row>
     <row r="10" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="145"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="152"/>
-      <c r="N10" s="145"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="129"/>
       <c r="O10" s="66"/>
     </row>
     <row r="11" spans="1:15" ht="15">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
       <c r="O11" s="74"/>
     </row>
     <row r="12" spans="1:15" s="76" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="147"/>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="144"/>
+      <c r="C12" s="144"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
       <c r="O12" s="75"/>
     </row>
     <row r="13" spans="1:15" s="76" customFormat="1" ht="140.1" customHeight="1" outlineLevel="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="131"/>
+      <c r="A13" s="162">
+        <v>1</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="131" t="s">
+        <v>55</v>
+      </c>
       <c r="E13" s="131"/>
       <c r="F13" s="131"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="23"/>
+      <c r="H13" s="84" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="20">
+        <v>46244</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="84" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>59</v>
+      </c>
       <c r="O13" s="75"/>
     </row>
     <row r="14" spans="1:15" s="76" customFormat="1" ht="9.9499999999999993" customHeight="1" outlineLevel="1">
-      <c r="A14" s="148"/>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-      <c r="L14" s="149"/>
-      <c r="M14" s="149"/>
-      <c r="N14" s="150"/>
+      <c r="A14" s="145"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="147"/>
     </row>
     <row r="15" spans="1:15" s="76" customFormat="1" ht="140.1" customHeight="1" outlineLevel="1">
-      <c r="A15" s="15"/>
+      <c r="A15" s="162"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="131"/>
@@ -2151,23 +2212,23 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:15" s="76" customFormat="1" ht="9.9499999999999993" customHeight="1" outlineLevel="1">
-      <c r="A16" s="116"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="118"/>
+      <c r="A16" s="123"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="125"/>
     </row>
     <row r="17" spans="1:14" s="76" customFormat="1" ht="140.1" customHeight="1" outlineLevel="1">
-      <c r="A17" s="15"/>
+      <c r="A17" s="162"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="131"/>
@@ -2183,20 +2244,20 @@
       <c r="N17" s="23"/>
     </row>
     <row r="18" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="118"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="125"/>
     </row>
     <row r="19" spans="1:14" ht="140.1" customHeight="1">
       <c r="A19" s="15"/>
@@ -2215,20 +2276,20 @@
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="117"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="117"/>
-      <c r="N20" s="118"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="125"/>
     </row>
     <row r="21" spans="1:14" ht="140.1" customHeight="1">
       <c r="A21" s="15"/>
@@ -2247,20 +2308,20 @@
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A22" s="116"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="118"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="124"/>
+      <c r="J22" s="124"/>
+      <c r="K22" s="124"/>
+      <c r="L22" s="124"/>
+      <c r="M22" s="124"/>
+      <c r="N22" s="125"/>
     </row>
     <row r="23" spans="1:14" ht="140.1" customHeight="1">
       <c r="A23" s="15"/>
@@ -2279,20 +2340,20 @@
       <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="117"/>
-      <c r="M24" s="117"/>
-      <c r="N24" s="118"/>
+      <c r="A24" s="123"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="125"/>
     </row>
     <row r="25" spans="1:14" ht="140.1" customHeight="1">
       <c r="A25" s="15"/>
@@ -2311,28 +2372,28 @@
       <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A26" s="116"/>
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="118"/>
+      <c r="A26" s="123"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="124"/>
+      <c r="L26" s="124"/>
+      <c r="M26" s="124"/>
+      <c r="N26" s="125"/>
     </row>
     <row r="27" spans="1:14" ht="140.1" customHeight="1">
       <c r="A27" s="15"/>
       <c r="B27" s="16"/>
       <c r="C27" s="17"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
       <c r="G27" s="19"/>
       <c r="H27" s="21"/>
       <c r="I27" s="25"/>
@@ -2343,28 +2404,28 @@
       <c r="N27" s="28"/>
     </row>
     <row r="28" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="125"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="127"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="127"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="128"/>
     </row>
     <row r="29" spans="1:14" ht="150" customHeight="1">
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="134"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="122"/>
       <c r="G29" s="19"/>
       <c r="H29" s="17"/>
       <c r="I29" s="20"/>
@@ -2375,28 +2436,28 @@
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A30" s="116"/>
-      <c r="B30" s="117"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="117"/>
-      <c r="N30" s="118"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="124"/>
+      <c r="I30" s="124"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="124"/>
+      <c r="L30" s="124"/>
+      <c r="M30" s="124"/>
+      <c r="N30" s="125"/>
     </row>
     <row r="31" spans="1:14" ht="150" customHeight="1">
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="132"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="134"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="122"/>
       <c r="G31" s="19"/>
       <c r="H31" s="24"/>
       <c r="I31" s="20"/>
@@ -2407,28 +2468,28 @@
       <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A32" s="116"/>
-      <c r="B32" s="117"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="117"/>
-      <c r="N32" s="118"/>
+      <c r="A32" s="123"/>
+      <c r="B32" s="124"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="124"/>
+      <c r="I32" s="124"/>
+      <c r="J32" s="124"/>
+      <c r="K32" s="124"/>
+      <c r="L32" s="124"/>
+      <c r="M32" s="124"/>
+      <c r="N32" s="125"/>
     </row>
     <row r="33" spans="1:14" ht="150" customHeight="1">
       <c r="A33" s="15"/>
       <c r="B33" s="16"/>
       <c r="C33" s="17"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="134"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="122"/>
       <c r="G33" s="19"/>
       <c r="H33" s="17"/>
       <c r="I33" s="20"/>
@@ -2439,28 +2500,28 @@
       <c r="N33" s="26"/>
     </row>
     <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A34" s="116"/>
-      <c r="B34" s="117"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="118"/>
+      <c r="A34" s="123"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="124"/>
+      <c r="I34" s="124"/>
+      <c r="J34" s="124"/>
+      <c r="K34" s="124"/>
+      <c r="L34" s="124"/>
+      <c r="M34" s="124"/>
+      <c r="N34" s="125"/>
     </row>
     <row r="35" spans="1:14" ht="150" customHeight="1">
       <c r="A35" s="15"/>
       <c r="B35" s="16"/>
       <c r="C35" s="17"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="134"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="122"/>
       <c r="G35" s="19"/>
       <c r="H35" s="17"/>
       <c r="I35" s="20"/>
@@ -2471,28 +2532,28 @@
       <c r="N35" s="28"/>
     </row>
     <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A36" s="116"/>
-      <c r="B36" s="117"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="118"/>
+      <c r="A36" s="123"/>
+      <c r="B36" s="124"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="124"/>
+      <c r="J36" s="124"/>
+      <c r="K36" s="124"/>
+      <c r="L36" s="124"/>
+      <c r="M36" s="124"/>
+      <c r="N36" s="125"/>
     </row>
     <row r="37" spans="1:14" ht="150" customHeight="1">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="17"/>
-      <c r="D37" s="132"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="134"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="122"/>
       <c r="G37" s="19"/>
       <c r="H37" s="17"/>
       <c r="I37" s="20"/>
@@ -2503,28 +2564,28 @@
       <c r="N37" s="26"/>
     </row>
     <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A38" s="116"/>
-      <c r="B38" s="117"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
-      <c r="I38" s="117"/>
-      <c r="J38" s="117"/>
-      <c r="K38" s="117"/>
-      <c r="L38" s="117"/>
-      <c r="M38" s="117"/>
-      <c r="N38" s="118"/>
+      <c r="A38" s="123"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="124"/>
+      <c r="D38" s="124"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="124"/>
+      <c r="H38" s="124"/>
+      <c r="I38" s="124"/>
+      <c r="J38" s="124"/>
+      <c r="K38" s="124"/>
+      <c r="L38" s="124"/>
+      <c r="M38" s="124"/>
+      <c r="N38" s="125"/>
     </row>
     <row r="39" spans="1:14" ht="150" customHeight="1">
       <c r="A39" s="15"/>
       <c r="B39" s="16"/>
       <c r="C39" s="17"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="134"/>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="122"/>
       <c r="G39" s="19"/>
       <c r="H39" s="17"/>
       <c r="I39" s="20"/>
@@ -2535,28 +2596,28 @@
       <c r="N39" s="26"/>
     </row>
     <row r="40" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A40" s="116"/>
-      <c r="B40" s="117"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="117"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="117"/>
-      <c r="J40" s="117"/>
-      <c r="K40" s="117"/>
-      <c r="L40" s="117"/>
-      <c r="M40" s="117"/>
-      <c r="N40" s="118"/>
+      <c r="A40" s="123"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="124"/>
+      <c r="D40" s="124"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="124"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="124"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="124"/>
+      <c r="L40" s="124"/>
+      <c r="M40" s="124"/>
+      <c r="N40" s="125"/>
     </row>
     <row r="41" spans="1:14" ht="150" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
       <c r="C41" s="17"/>
-      <c r="D41" s="132"/>
-      <c r="E41" s="133"/>
-      <c r="F41" s="134"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="122"/>
       <c r="G41" s="19"/>
       <c r="H41" s="17"/>
       <c r="I41" s="20"/>
@@ -2567,28 +2628,28 @@
       <c r="N41" s="26"/>
     </row>
     <row r="42" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A42" s="116"/>
-      <c r="B42" s="117"/>
-      <c r="C42" s="117"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="117"/>
-      <c r="F42" s="117"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="117"/>
-      <c r="I42" s="117"/>
-      <c r="J42" s="117"/>
-      <c r="K42" s="117"/>
-      <c r="L42" s="117"/>
-      <c r="M42" s="117"/>
-      <c r="N42" s="118"/>
+      <c r="A42" s="123"/>
+      <c r="B42" s="124"/>
+      <c r="C42" s="124"/>
+      <c r="D42" s="124"/>
+      <c r="E42" s="124"/>
+      <c r="F42" s="124"/>
+      <c r="G42" s="124"/>
+      <c r="H42" s="124"/>
+      <c r="I42" s="124"/>
+      <c r="J42" s="124"/>
+      <c r="K42" s="124"/>
+      <c r="L42" s="124"/>
+      <c r="M42" s="124"/>
+      <c r="N42" s="125"/>
     </row>
     <row r="43" spans="1:14" ht="150" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="17"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="134"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="122"/>
       <c r="G43" s="19"/>
       <c r="H43" s="21"/>
       <c r="I43" s="20"/>
@@ -2599,28 +2660,28 @@
       <c r="N43" s="28"/>
     </row>
     <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A44" s="116"/>
-      <c r="B44" s="117"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="117"/>
-      <c r="I44" s="117"/>
-      <c r="J44" s="117"/>
-      <c r="K44" s="117"/>
-      <c r="L44" s="117"/>
-      <c r="M44" s="117"/>
-      <c r="N44" s="118"/>
+      <c r="A44" s="123"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="124"/>
+      <c r="D44" s="124"/>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="124"/>
+      <c r="H44" s="124"/>
+      <c r="I44" s="124"/>
+      <c r="J44" s="124"/>
+      <c r="K44" s="124"/>
+      <c r="L44" s="124"/>
+      <c r="M44" s="124"/>
+      <c r="N44" s="125"/>
     </row>
     <row r="45" spans="1:14" ht="150" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="16"/>
       <c r="C45" s="17"/>
-      <c r="D45" s="132"/>
-      <c r="E45" s="133"/>
-      <c r="F45" s="134"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="122"/>
       <c r="G45" s="19"/>
       <c r="H45" s="21"/>
       <c r="I45" s="20"/>
@@ -2631,28 +2692,28 @@
       <c r="N45" s="28"/>
     </row>
     <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A46" s="116"/>
-      <c r="B46" s="117"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="117"/>
-      <c r="G46" s="117"/>
-      <c r="H46" s="117"/>
-      <c r="I46" s="117"/>
-      <c r="J46" s="117"/>
-      <c r="K46" s="117"/>
-      <c r="L46" s="117"/>
-      <c r="M46" s="117"/>
-      <c r="N46" s="118"/>
+      <c r="A46" s="123"/>
+      <c r="B46" s="124"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="124"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="124"/>
+      <c r="G46" s="124"/>
+      <c r="H46" s="124"/>
+      <c r="I46" s="124"/>
+      <c r="J46" s="124"/>
+      <c r="K46" s="124"/>
+      <c r="L46" s="124"/>
+      <c r="M46" s="124"/>
+      <c r="N46" s="125"/>
     </row>
     <row r="47" spans="1:14" ht="150" customHeight="1">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="17"/>
-      <c r="D47" s="132"/>
-      <c r="E47" s="133"/>
-      <c r="F47" s="134"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="122"/>
       <c r="G47" s="19"/>
       <c r="H47" s="21"/>
       <c r="I47" s="20"/>
@@ -2663,28 +2724,28 @@
       <c r="N47" s="26"/>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A48" s="116"/>
-      <c r="B48" s="117"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117"/>
-      <c r="H48" s="117"/>
-      <c r="I48" s="117"/>
-      <c r="J48" s="117"/>
-      <c r="K48" s="117"/>
-      <c r="L48" s="117"/>
-      <c r="M48" s="117"/>
-      <c r="N48" s="118"/>
+      <c r="A48" s="123"/>
+      <c r="B48" s="124"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="124"/>
+      <c r="F48" s="124"/>
+      <c r="G48" s="124"/>
+      <c r="H48" s="124"/>
+      <c r="I48" s="124"/>
+      <c r="J48" s="124"/>
+      <c r="K48" s="124"/>
+      <c r="L48" s="124"/>
+      <c r="M48" s="124"/>
+      <c r="N48" s="125"/>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="15"/>
       <c r="B49" s="16"/>
       <c r="C49" s="17"/>
-      <c r="D49" s="132"/>
-      <c r="E49" s="133"/>
-      <c r="F49" s="134"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="122"/>
       <c r="G49" s="19"/>
       <c r="H49" s="21"/>
       <c r="I49" s="20"/>
@@ -2695,28 +2756,28 @@
       <c r="N49" s="26"/>
     </row>
     <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A50" s="116"/>
-      <c r="B50" s="117"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="117"/>
-      <c r="J50" s="117"/>
-      <c r="K50" s="117"/>
-      <c r="L50" s="117"/>
-      <c r="M50" s="117"/>
-      <c r="N50" s="118"/>
+      <c r="A50" s="123"/>
+      <c r="B50" s="124"/>
+      <c r="C50" s="124"/>
+      <c r="D50" s="124"/>
+      <c r="E50" s="124"/>
+      <c r="F50" s="124"/>
+      <c r="G50" s="124"/>
+      <c r="H50" s="124"/>
+      <c r="I50" s="124"/>
+      <c r="J50" s="124"/>
+      <c r="K50" s="124"/>
+      <c r="L50" s="124"/>
+      <c r="M50" s="124"/>
+      <c r="N50" s="125"/>
     </row>
     <row r="51" spans="1:14" ht="150" customHeight="1">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="17"/>
-      <c r="D51" s="132"/>
-      <c r="E51" s="133"/>
-      <c r="F51" s="134"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="122"/>
       <c r="G51" s="19"/>
       <c r="H51" s="21"/>
       <c r="I51" s="20"/>
@@ -2727,28 +2788,28 @@
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="125"/>
-      <c r="B52" s="126"/>
-      <c r="C52" s="126"/>
-      <c r="D52" s="126"/>
-      <c r="E52" s="126"/>
-      <c r="F52" s="126"/>
-      <c r="G52" s="126"/>
-      <c r="H52" s="126"/>
-      <c r="I52" s="126"/>
-      <c r="J52" s="126"/>
-      <c r="K52" s="126"/>
-      <c r="L52" s="126"/>
-      <c r="M52" s="126"/>
-      <c r="N52" s="127"/>
+      <c r="A52" s="126"/>
+      <c r="B52" s="127"/>
+      <c r="C52" s="127"/>
+      <c r="D52" s="127"/>
+      <c r="E52" s="127"/>
+      <c r="F52" s="127"/>
+      <c r="G52" s="127"/>
+      <c r="H52" s="127"/>
+      <c r="I52" s="127"/>
+      <c r="J52" s="127"/>
+      <c r="K52" s="127"/>
+      <c r="L52" s="127"/>
+      <c r="M52" s="127"/>
+      <c r="N52" s="128"/>
     </row>
     <row r="53" spans="1:14" ht="140.1" customHeight="1">
       <c r="A53" s="15"/>
       <c r="B53" s="16"/>
       <c r="C53" s="17"/>
-      <c r="D53" s="132"/>
-      <c r="E53" s="133"/>
-      <c r="F53" s="134"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="122"/>
       <c r="G53" s="19"/>
       <c r="H53" s="17"/>
       <c r="I53" s="20"/>
@@ -2759,28 +2820,28 @@
       <c r="N53" s="26"/>
     </row>
     <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A54" s="116"/>
-      <c r="B54" s="117"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="117"/>
-      <c r="F54" s="117"/>
-      <c r="G54" s="117"/>
-      <c r="H54" s="117"/>
-      <c r="I54" s="117"/>
-      <c r="J54" s="117"/>
-      <c r="K54" s="117"/>
-      <c r="L54" s="117"/>
-      <c r="M54" s="117"/>
-      <c r="N54" s="118"/>
+      <c r="A54" s="123"/>
+      <c r="B54" s="124"/>
+      <c r="C54" s="124"/>
+      <c r="D54" s="124"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="124"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="124"/>
+      <c r="I54" s="124"/>
+      <c r="J54" s="124"/>
+      <c r="K54" s="124"/>
+      <c r="L54" s="124"/>
+      <c r="M54" s="124"/>
+      <c r="N54" s="125"/>
     </row>
     <row r="55" spans="1:14" ht="146.25" customHeight="1">
       <c r="A55" s="15"/>
       <c r="B55" s="16"/>
       <c r="C55" s="17"/>
-      <c r="D55" s="132"/>
-      <c r="E55" s="133"/>
-      <c r="F55" s="134"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="122"/>
       <c r="G55" s="19"/>
       <c r="H55" s="24"/>
       <c r="I55" s="20"/>
@@ -2791,28 +2852,28 @@
       <c r="N55" s="42"/>
     </row>
     <row r="56" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A56" s="116"/>
-      <c r="B56" s="117"/>
-      <c r="C56" s="117"/>
-      <c r="D56" s="117"/>
-      <c r="E56" s="117"/>
-      <c r="F56" s="117"/>
-      <c r="G56" s="117"/>
-      <c r="H56" s="117"/>
-      <c r="I56" s="117"/>
-      <c r="J56" s="117"/>
-      <c r="K56" s="117"/>
-      <c r="L56" s="117"/>
-      <c r="M56" s="117"/>
-      <c r="N56" s="118"/>
+      <c r="A56" s="123"/>
+      <c r="B56" s="124"/>
+      <c r="C56" s="124"/>
+      <c r="D56" s="124"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="124"/>
+      <c r="H56" s="124"/>
+      <c r="I56" s="124"/>
+      <c r="J56" s="124"/>
+      <c r="K56" s="124"/>
+      <c r="L56" s="124"/>
+      <c r="M56" s="124"/>
+      <c r="N56" s="125"/>
     </row>
     <row r="57" spans="1:14" ht="149.25" customHeight="1">
       <c r="A57" s="15"/>
       <c r="B57" s="16"/>
       <c r="C57" s="17"/>
-      <c r="D57" s="132"/>
-      <c r="E57" s="133"/>
-      <c r="F57" s="134"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="122"/>
       <c r="G57" s="19"/>
       <c r="H57" s="17"/>
       <c r="I57" s="20"/>
@@ -2823,28 +2884,28 @@
       <c r="N57" s="42"/>
     </row>
     <row r="58" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="125"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="126"/>
-      <c r="D58" s="126"/>
-      <c r="E58" s="126"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="126"/>
-      <c r="H58" s="126"/>
-      <c r="I58" s="126"/>
-      <c r="J58" s="126"/>
-      <c r="K58" s="126"/>
-      <c r="L58" s="126"/>
-      <c r="M58" s="126"/>
-      <c r="N58" s="127"/>
+      <c r="A58" s="126"/>
+      <c r="B58" s="127"/>
+      <c r="C58" s="127"/>
+      <c r="D58" s="127"/>
+      <c r="E58" s="127"/>
+      <c r="F58" s="127"/>
+      <c r="G58" s="127"/>
+      <c r="H58" s="127"/>
+      <c r="I58" s="127"/>
+      <c r="J58" s="127"/>
+      <c r="K58" s="127"/>
+      <c r="L58" s="127"/>
+      <c r="M58" s="127"/>
+      <c r="N58" s="128"/>
     </row>
     <row r="59" spans="1:14" ht="144" customHeight="1">
       <c r="A59" s="15"/>
       <c r="B59" s="16"/>
       <c r="C59" s="17"/>
-      <c r="D59" s="132"/>
-      <c r="E59" s="133"/>
-      <c r="F59" s="134"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="122"/>
       <c r="G59" s="19"/>
       <c r="H59" s="17"/>
       <c r="I59" s="20"/>
@@ -2855,28 +2916,28 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A60" s="116"/>
-      <c r="B60" s="117"/>
-      <c r="C60" s="117"/>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="117"/>
-      <c r="L60" s="117"/>
-      <c r="M60" s="117"/>
-      <c r="N60" s="118"/>
+      <c r="A60" s="123"/>
+      <c r="B60" s="124"/>
+      <c r="C60" s="124"/>
+      <c r="D60" s="124"/>
+      <c r="E60" s="124"/>
+      <c r="F60" s="124"/>
+      <c r="G60" s="124"/>
+      <c r="H60" s="124"/>
+      <c r="I60" s="124"/>
+      <c r="J60" s="124"/>
+      <c r="K60" s="124"/>
+      <c r="L60" s="124"/>
+      <c r="M60" s="124"/>
+      <c r="N60" s="125"/>
     </row>
     <row r="61" spans="1:14" ht="162.75" customHeight="1">
       <c r="A61" s="15"/>
       <c r="B61" s="16"/>
       <c r="C61" s="17"/>
-      <c r="D61" s="132"/>
-      <c r="E61" s="133"/>
-      <c r="F61" s="134"/>
+      <c r="D61" s="120"/>
+      <c r="E61" s="121"/>
+      <c r="F61" s="122"/>
       <c r="G61" s="19"/>
       <c r="H61" s="30"/>
       <c r="I61" s="20"/>
@@ -2887,28 +2948,28 @@
       <c r="N61" s="26"/>
     </row>
     <row r="62" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A62" s="116"/>
-      <c r="B62" s="117"/>
-      <c r="C62" s="117"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="117"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="117"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
-      <c r="J62" s="117"/>
-      <c r="K62" s="117"/>
-      <c r="L62" s="117"/>
-      <c r="M62" s="117"/>
-      <c r="N62" s="118"/>
+      <c r="A62" s="123"/>
+      <c r="B62" s="124"/>
+      <c r="C62" s="124"/>
+      <c r="D62" s="124"/>
+      <c r="E62" s="124"/>
+      <c r="F62" s="124"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="124"/>
+      <c r="I62" s="124"/>
+      <c r="J62" s="124"/>
+      <c r="K62" s="124"/>
+      <c r="L62" s="124"/>
+      <c r="M62" s="124"/>
+      <c r="N62" s="125"/>
     </row>
     <row r="63" spans="1:14" ht="168.75" customHeight="1">
       <c r="A63" s="15"/>
       <c r="B63" s="16"/>
       <c r="C63" s="17"/>
-      <c r="D63" s="132"/>
-      <c r="E63" s="133"/>
-      <c r="F63" s="134"/>
+      <c r="D63" s="120"/>
+      <c r="E63" s="121"/>
+      <c r="F63" s="122"/>
       <c r="G63" s="19"/>
       <c r="H63" s="17"/>
       <c r="I63" s="20"/>
@@ -2919,28 +2980,28 @@
       <c r="N63" s="26"/>
     </row>
     <row r="64" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A64" s="116"/>
-      <c r="B64" s="117"/>
-      <c r="C64" s="117"/>
-      <c r="D64" s="117"/>
-      <c r="E64" s="117"/>
-      <c r="F64" s="117"/>
-      <c r="G64" s="117"/>
-      <c r="H64" s="117"/>
-      <c r="I64" s="117"/>
-      <c r="J64" s="117"/>
-      <c r="K64" s="117"/>
-      <c r="L64" s="117"/>
-      <c r="M64" s="117"/>
-      <c r="N64" s="118"/>
+      <c r="A64" s="123"/>
+      <c r="B64" s="124"/>
+      <c r="C64" s="124"/>
+      <c r="D64" s="124"/>
+      <c r="E64" s="124"/>
+      <c r="F64" s="124"/>
+      <c r="G64" s="124"/>
+      <c r="H64" s="124"/>
+      <c r="I64" s="124"/>
+      <c r="J64" s="124"/>
+      <c r="K64" s="124"/>
+      <c r="L64" s="124"/>
+      <c r="M64" s="124"/>
+      <c r="N64" s="125"/>
     </row>
     <row r="65" spans="1:14" ht="162.75" customHeight="1">
       <c r="A65" s="15"/>
       <c r="B65" s="16"/>
       <c r="C65" s="17"/>
-      <c r="D65" s="132"/>
-      <c r="E65" s="133"/>
-      <c r="F65" s="134"/>
+      <c r="D65" s="120"/>
+      <c r="E65" s="121"/>
+      <c r="F65" s="122"/>
       <c r="G65" s="19"/>
       <c r="H65" s="17"/>
       <c r="I65" s="20"/>
@@ -2951,28 +3012,28 @@
       <c r="N65" s="26"/>
     </row>
     <row r="66" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A66" s="116"/>
-      <c r="B66" s="117"/>
-      <c r="C66" s="117"/>
-      <c r="D66" s="117"/>
-      <c r="E66" s="117"/>
-      <c r="F66" s="117"/>
-      <c r="G66" s="117"/>
-      <c r="H66" s="117"/>
-      <c r="I66" s="117"/>
-      <c r="J66" s="117"/>
-      <c r="K66" s="117"/>
-      <c r="L66" s="117"/>
-      <c r="M66" s="117"/>
-      <c r="N66" s="118"/>
+      <c r="A66" s="123"/>
+      <c r="B66" s="124"/>
+      <c r="C66" s="124"/>
+      <c r="D66" s="124"/>
+      <c r="E66" s="124"/>
+      <c r="F66" s="124"/>
+      <c r="G66" s="124"/>
+      <c r="H66" s="124"/>
+      <c r="I66" s="124"/>
+      <c r="J66" s="124"/>
+      <c r="K66" s="124"/>
+      <c r="L66" s="124"/>
+      <c r="M66" s="124"/>
+      <c r="N66" s="125"/>
     </row>
     <row r="67" spans="1:14" ht="156" customHeight="1">
       <c r="A67" s="15"/>
       <c r="B67" s="16"/>
       <c r="C67" s="17"/>
-      <c r="D67" s="132"/>
-      <c r="E67" s="133"/>
-      <c r="F67" s="134"/>
+      <c r="D67" s="120"/>
+      <c r="E67" s="121"/>
+      <c r="F67" s="122"/>
       <c r="G67" s="19"/>
       <c r="H67" s="21"/>
       <c r="I67" s="20"/>
@@ -2983,28 +3044,28 @@
       <c r="N67" s="26"/>
     </row>
     <row r="68" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A68" s="125"/>
-      <c r="B68" s="126"/>
-      <c r="C68" s="126"/>
-      <c r="D68" s="126"/>
-      <c r="E68" s="126"/>
-      <c r="F68" s="126"/>
-      <c r="G68" s="126"/>
-      <c r="H68" s="126"/>
-      <c r="I68" s="126"/>
-      <c r="J68" s="126"/>
-      <c r="K68" s="126"/>
-      <c r="L68" s="126"/>
-      <c r="M68" s="126"/>
-      <c r="N68" s="127"/>
+      <c r="A68" s="126"/>
+      <c r="B68" s="127"/>
+      <c r="C68" s="127"/>
+      <c r="D68" s="127"/>
+      <c r="E68" s="127"/>
+      <c r="F68" s="127"/>
+      <c r="G68" s="127"/>
+      <c r="H68" s="127"/>
+      <c r="I68" s="127"/>
+      <c r="J68" s="127"/>
+      <c r="K68" s="127"/>
+      <c r="L68" s="127"/>
+      <c r="M68" s="127"/>
+      <c r="N68" s="128"/>
     </row>
     <row r="69" spans="1:14" ht="168.75" customHeight="1">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="17"/>
-      <c r="D69" s="132"/>
-      <c r="E69" s="133"/>
-      <c r="F69" s="134"/>
+      <c r="D69" s="120"/>
+      <c r="E69" s="121"/>
+      <c r="F69" s="122"/>
       <c r="G69" s="19"/>
       <c r="H69" s="21"/>
       <c r="I69" s="20"/>
@@ -3015,28 +3076,28 @@
       <c r="N69" s="26"/>
     </row>
     <row r="70" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A70" s="116"/>
-      <c r="B70" s="117"/>
-      <c r="C70" s="117"/>
-      <c r="D70" s="117"/>
-      <c r="E70" s="117"/>
-      <c r="F70" s="117"/>
-      <c r="G70" s="117"/>
-      <c r="H70" s="117"/>
-      <c r="I70" s="117"/>
-      <c r="J70" s="117"/>
-      <c r="K70" s="117"/>
-      <c r="L70" s="117"/>
-      <c r="M70" s="117"/>
-      <c r="N70" s="118"/>
+      <c r="A70" s="123"/>
+      <c r="B70" s="124"/>
+      <c r="C70" s="124"/>
+      <c r="D70" s="124"/>
+      <c r="E70" s="124"/>
+      <c r="F70" s="124"/>
+      <c r="G70" s="124"/>
+      <c r="H70" s="124"/>
+      <c r="I70" s="124"/>
+      <c r="J70" s="124"/>
+      <c r="K70" s="124"/>
+      <c r="L70" s="124"/>
+      <c r="M70" s="124"/>
+      <c r="N70" s="125"/>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="15"/>
       <c r="B71" s="16"/>
       <c r="C71" s="17"/>
-      <c r="D71" s="132"/>
-      <c r="E71" s="133"/>
-      <c r="F71" s="134"/>
+      <c r="D71" s="120"/>
+      <c r="E71" s="121"/>
+      <c r="F71" s="122"/>
       <c r="G71" s="19"/>
       <c r="H71" s="21"/>
       <c r="I71" s="20"/>
@@ -3047,28 +3108,28 @@
       <c r="N71" s="26"/>
     </row>
     <row r="72" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A72" s="116"/>
-      <c r="B72" s="117"/>
-      <c r="C72" s="117"/>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="117"/>
-      <c r="I72" s="117"/>
-      <c r="J72" s="117"/>
-      <c r="K72" s="117"/>
-      <c r="L72" s="117"/>
-      <c r="M72" s="117"/>
-      <c r="N72" s="118"/>
+      <c r="A72" s="123"/>
+      <c r="B72" s="124"/>
+      <c r="C72" s="124"/>
+      <c r="D72" s="124"/>
+      <c r="E72" s="124"/>
+      <c r="F72" s="124"/>
+      <c r="G72" s="124"/>
+      <c r="H72" s="124"/>
+      <c r="I72" s="124"/>
+      <c r="J72" s="124"/>
+      <c r="K72" s="124"/>
+      <c r="L72" s="124"/>
+      <c r="M72" s="124"/>
+      <c r="N72" s="125"/>
     </row>
     <row r="73" spans="1:14" ht="170.25" customHeight="1">
       <c r="A73" s="15"/>
       <c r="B73" s="16"/>
       <c r="C73" s="17"/>
-      <c r="D73" s="132"/>
-      <c r="E73" s="133"/>
-      <c r="F73" s="134"/>
+      <c r="D73" s="120"/>
+      <c r="E73" s="121"/>
+      <c r="F73" s="122"/>
       <c r="G73" s="19"/>
       <c r="H73" s="21"/>
       <c r="I73" s="20"/>
@@ -3079,28 +3140,28 @@
       <c r="N73" s="26"/>
     </row>
     <row r="74" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A74" s="116"/>
-      <c r="B74" s="117"/>
-      <c r="C74" s="117"/>
-      <c r="D74" s="117"/>
-      <c r="E74" s="117"/>
-      <c r="F74" s="117"/>
-      <c r="G74" s="117"/>
-      <c r="H74" s="117"/>
-      <c r="I74" s="117"/>
-      <c r="J74" s="117"/>
-      <c r="K74" s="117"/>
-      <c r="L74" s="117"/>
-      <c r="M74" s="117"/>
-      <c r="N74" s="118"/>
+      <c r="A74" s="123"/>
+      <c r="B74" s="124"/>
+      <c r="C74" s="124"/>
+      <c r="D74" s="124"/>
+      <c r="E74" s="124"/>
+      <c r="F74" s="124"/>
+      <c r="G74" s="124"/>
+      <c r="H74" s="124"/>
+      <c r="I74" s="124"/>
+      <c r="J74" s="124"/>
+      <c r="K74" s="124"/>
+      <c r="L74" s="124"/>
+      <c r="M74" s="124"/>
+      <c r="N74" s="125"/>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="15"/>
       <c r="B75" s="16"/>
       <c r="C75" s="17"/>
-      <c r="D75" s="132"/>
-      <c r="E75" s="133"/>
-      <c r="F75" s="134"/>
+      <c r="D75" s="120"/>
+      <c r="E75" s="121"/>
+      <c r="F75" s="122"/>
       <c r="G75" s="19"/>
       <c r="H75" s="21"/>
       <c r="I75" s="20"/>
@@ -3111,28 +3172,28 @@
       <c r="N75" s="26"/>
     </row>
     <row r="76" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A76" s="116"/>
-      <c r="B76" s="117"/>
-      <c r="C76" s="117"/>
-      <c r="D76" s="117"/>
-      <c r="E76" s="117"/>
-      <c r="F76" s="117"/>
-      <c r="G76" s="117"/>
-      <c r="H76" s="117"/>
-      <c r="I76" s="117"/>
-      <c r="J76" s="117"/>
-      <c r="K76" s="117"/>
-      <c r="L76" s="117"/>
-      <c r="M76" s="117"/>
-      <c r="N76" s="118"/>
+      <c r="A76" s="123"/>
+      <c r="B76" s="124"/>
+      <c r="C76" s="124"/>
+      <c r="D76" s="124"/>
+      <c r="E76" s="124"/>
+      <c r="F76" s="124"/>
+      <c r="G76" s="124"/>
+      <c r="H76" s="124"/>
+      <c r="I76" s="124"/>
+      <c r="J76" s="124"/>
+      <c r="K76" s="124"/>
+      <c r="L76" s="124"/>
+      <c r="M76" s="124"/>
+      <c r="N76" s="125"/>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="15"/>
       <c r="B77" s="16"/>
       <c r="C77" s="17"/>
-      <c r="D77" s="132"/>
-      <c r="E77" s="133"/>
-      <c r="F77" s="134"/>
+      <c r="D77" s="120"/>
+      <c r="E77" s="121"/>
+      <c r="F77" s="122"/>
       <c r="G77" s="19"/>
       <c r="H77" s="21"/>
       <c r="I77" s="20"/>
@@ -3143,28 +3204,28 @@
       <c r="N77" s="26"/>
     </row>
     <row r="78" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A78" s="116"/>
-      <c r="B78" s="117"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="117"/>
-      <c r="E78" s="117"/>
-      <c r="F78" s="117"/>
-      <c r="G78" s="117"/>
-      <c r="H78" s="117"/>
-      <c r="I78" s="117"/>
-      <c r="J78" s="117"/>
-      <c r="K78" s="117"/>
-      <c r="L78" s="117"/>
-      <c r="M78" s="117"/>
-      <c r="N78" s="118"/>
+      <c r="A78" s="123"/>
+      <c r="B78" s="124"/>
+      <c r="C78" s="124"/>
+      <c r="D78" s="124"/>
+      <c r="E78" s="124"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="124"/>
+      <c r="H78" s="124"/>
+      <c r="I78" s="124"/>
+      <c r="J78" s="124"/>
+      <c r="K78" s="124"/>
+      <c r="L78" s="124"/>
+      <c r="M78" s="124"/>
+      <c r="N78" s="125"/>
     </row>
     <row r="79" spans="1:14" ht="151.5" customHeight="1">
       <c r="A79" s="15"/>
       <c r="B79" s="16"/>
       <c r="C79" s="17"/>
-      <c r="D79" s="132"/>
-      <c r="E79" s="133"/>
-      <c r="F79" s="134"/>
+      <c r="D79" s="120"/>
+      <c r="E79" s="121"/>
+      <c r="F79" s="122"/>
       <c r="G79" s="19"/>
       <c r="H79" s="21"/>
       <c r="I79" s="20"/>
@@ -3175,28 +3236,28 @@
       <c r="N79" s="26"/>
     </row>
     <row r="80" spans="1:14" ht="21" customHeight="1">
-      <c r="A80" s="125"/>
-      <c r="B80" s="126"/>
-      <c r="C80" s="126"/>
-      <c r="D80" s="126"/>
-      <c r="E80" s="126"/>
-      <c r="F80" s="126"/>
-      <c r="G80" s="126"/>
-      <c r="H80" s="126"/>
-      <c r="I80" s="126"/>
-      <c r="J80" s="126"/>
-      <c r="K80" s="126"/>
-      <c r="L80" s="126"/>
-      <c r="M80" s="126"/>
-      <c r="N80" s="127"/>
+      <c r="A80" s="126"/>
+      <c r="B80" s="127"/>
+      <c r="C80" s="127"/>
+      <c r="D80" s="127"/>
+      <c r="E80" s="127"/>
+      <c r="F80" s="127"/>
+      <c r="G80" s="127"/>
+      <c r="H80" s="127"/>
+      <c r="I80" s="127"/>
+      <c r="J80" s="127"/>
+      <c r="K80" s="127"/>
+      <c r="L80" s="127"/>
+      <c r="M80" s="127"/>
+      <c r="N80" s="128"/>
     </row>
     <row r="81" spans="1:14" ht="140.1" customHeight="1">
       <c r="A81" s="16"/>
       <c r="B81" s="18"/>
       <c r="C81" s="17"/>
-      <c r="D81" s="128"/>
-      <c r="E81" s="129"/>
-      <c r="F81" s="130"/>
+      <c r="D81" s="154"/>
+      <c r="E81" s="155"/>
+      <c r="F81" s="156"/>
       <c r="G81" s="19"/>
       <c r="H81" s="21"/>
       <c r="I81" s="20"/>
@@ -3207,28 +3268,28 @@
       <c r="N81" s="26"/>
     </row>
     <row r="82" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A82" s="116"/>
-      <c r="B82" s="117"/>
-      <c r="C82" s="117"/>
-      <c r="D82" s="117"/>
-      <c r="E82" s="117"/>
-      <c r="F82" s="117"/>
-      <c r="G82" s="117"/>
-      <c r="H82" s="117"/>
-      <c r="I82" s="117"/>
-      <c r="J82" s="117"/>
-      <c r="K82" s="117"/>
-      <c r="L82" s="117"/>
-      <c r="M82" s="117"/>
-      <c r="N82" s="118"/>
+      <c r="A82" s="123"/>
+      <c r="B82" s="124"/>
+      <c r="C82" s="124"/>
+      <c r="D82" s="124"/>
+      <c r="E82" s="124"/>
+      <c r="F82" s="124"/>
+      <c r="G82" s="124"/>
+      <c r="H82" s="124"/>
+      <c r="I82" s="124"/>
+      <c r="J82" s="124"/>
+      <c r="K82" s="124"/>
+      <c r="L82" s="124"/>
+      <c r="M82" s="124"/>
+      <c r="N82" s="125"/>
     </row>
     <row r="83" spans="1:14" ht="140.1" customHeight="1">
       <c r="A83" s="15"/>
       <c r="B83" s="18"/>
       <c r="C83" s="17"/>
-      <c r="D83" s="128"/>
-      <c r="E83" s="129"/>
-      <c r="F83" s="130"/>
+      <c r="D83" s="154"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="156"/>
       <c r="G83" s="19"/>
       <c r="H83" s="21"/>
       <c r="I83" s="20"/>
@@ -3239,20 +3300,20 @@
       <c r="N83" s="26"/>
     </row>
     <row r="84" spans="1:14" ht="9.75" customHeight="1">
-      <c r="A84" s="116"/>
-      <c r="B84" s="117"/>
-      <c r="C84" s="117"/>
-      <c r="D84" s="117"/>
-      <c r="E84" s="117"/>
-      <c r="F84" s="117"/>
-      <c r="G84" s="117"/>
-      <c r="H84" s="117"/>
-      <c r="I84" s="117"/>
-      <c r="J84" s="117"/>
-      <c r="K84" s="117"/>
-      <c r="L84" s="117"/>
-      <c r="M84" s="117"/>
-      <c r="N84" s="118"/>
+      <c r="A84" s="123"/>
+      <c r="B84" s="124"/>
+      <c r="C84" s="124"/>
+      <c r="D84" s="124"/>
+      <c r="E84" s="124"/>
+      <c r="F84" s="124"/>
+      <c r="G84" s="124"/>
+      <c r="H84" s="124"/>
+      <c r="I84" s="124"/>
+      <c r="J84" s="124"/>
+      <c r="K84" s="124"/>
+      <c r="L84" s="124"/>
+      <c r="M84" s="124"/>
+      <c r="N84" s="125"/>
     </row>
     <row r="85" spans="1:14" ht="140.1" customHeight="1">
       <c r="A85" s="15"/>
@@ -3271,28 +3332,28 @@
       <c r="N85" s="26"/>
     </row>
     <row r="86" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A86" s="116"/>
-      <c r="B86" s="117"/>
-      <c r="C86" s="117"/>
-      <c r="D86" s="117"/>
-      <c r="E86" s="117"/>
-      <c r="F86" s="117"/>
-      <c r="G86" s="117"/>
-      <c r="H86" s="117"/>
-      <c r="I86" s="117"/>
-      <c r="J86" s="117"/>
-      <c r="K86" s="117"/>
-      <c r="L86" s="117"/>
-      <c r="M86" s="117"/>
-      <c r="N86" s="118"/>
+      <c r="A86" s="123"/>
+      <c r="B86" s="124"/>
+      <c r="C86" s="124"/>
+      <c r="D86" s="124"/>
+      <c r="E86" s="124"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="124"/>
+      <c r="H86" s="124"/>
+      <c r="I86" s="124"/>
+      <c r="J86" s="124"/>
+      <c r="K86" s="124"/>
+      <c r="L86" s="124"/>
+      <c r="M86" s="124"/>
+      <c r="N86" s="125"/>
     </row>
     <row r="87" spans="1:14" ht="140.1" customHeight="1">
       <c r="A87" s="26"/>
       <c r="B87" s="28"/>
       <c r="C87" s="42"/>
-      <c r="D87" s="122"/>
-      <c r="E87" s="123"/>
-      <c r="F87" s="124"/>
+      <c r="D87" s="151"/>
+      <c r="E87" s="152"/>
+      <c r="F87" s="153"/>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
       <c r="I87" s="81"/>
@@ -3303,28 +3364,28 @@
       <c r="N87" s="26"/>
     </row>
     <row r="88" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A88" s="116"/>
-      <c r="B88" s="117"/>
-      <c r="C88" s="117"/>
-      <c r="D88" s="117"/>
-      <c r="E88" s="117"/>
-      <c r="F88" s="117"/>
-      <c r="G88" s="117"/>
-      <c r="H88" s="117"/>
-      <c r="I88" s="117"/>
-      <c r="J88" s="117"/>
-      <c r="K88" s="117"/>
-      <c r="L88" s="117"/>
-      <c r="M88" s="117"/>
-      <c r="N88" s="118"/>
+      <c r="A88" s="123"/>
+      <c r="B88" s="124"/>
+      <c r="C88" s="124"/>
+      <c r="D88" s="124"/>
+      <c r="E88" s="124"/>
+      <c r="F88" s="124"/>
+      <c r="G88" s="124"/>
+      <c r="H88" s="124"/>
+      <c r="I88" s="124"/>
+      <c r="J88" s="124"/>
+      <c r="K88" s="124"/>
+      <c r="L88" s="124"/>
+      <c r="M88" s="124"/>
+      <c r="N88" s="125"/>
     </row>
     <row r="89" spans="1:14" ht="140.1" customHeight="1">
       <c r="A89" s="26"/>
       <c r="B89" s="28"/>
       <c r="C89" s="42"/>
-      <c r="D89" s="122"/>
-      <c r="E89" s="123"/>
-      <c r="F89" s="124"/>
+      <c r="D89" s="151"/>
+      <c r="E89" s="152"/>
+      <c r="F89" s="153"/>
       <c r="G89" s="30"/>
       <c r="H89" s="30"/>
       <c r="I89" s="81"/>
@@ -3335,28 +3396,28 @@
       <c r="N89" s="26"/>
     </row>
     <row r="90" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A90" s="119"/>
-      <c r="B90" s="120"/>
-      <c r="C90" s="120"/>
-      <c r="D90" s="120"/>
-      <c r="E90" s="120"/>
-      <c r="F90" s="120"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="120"/>
-      <c r="I90" s="120"/>
-      <c r="J90" s="120"/>
-      <c r="K90" s="120"/>
-      <c r="L90" s="120"/>
-      <c r="M90" s="120"/>
-      <c r="N90" s="121"/>
+      <c r="A90" s="148"/>
+      <c r="B90" s="149"/>
+      <c r="C90" s="149"/>
+      <c r="D90" s="149"/>
+      <c r="E90" s="149"/>
+      <c r="F90" s="149"/>
+      <c r="G90" s="149"/>
+      <c r="H90" s="149"/>
+      <c r="I90" s="149"/>
+      <c r="J90" s="149"/>
+      <c r="K90" s="149"/>
+      <c r="L90" s="149"/>
+      <c r="M90" s="149"/>
+      <c r="N90" s="150"/>
     </row>
     <row r="91" spans="1:14" ht="119.25" customHeight="1">
       <c r="A91" s="26"/>
       <c r="B91" s="28"/>
       <c r="C91" s="42"/>
-      <c r="D91" s="122"/>
-      <c r="E91" s="123"/>
-      <c r="F91" s="124"/>
+      <c r="D91" s="151"/>
+      <c r="E91" s="152"/>
+      <c r="F91" s="153"/>
       <c r="G91" s="30"/>
       <c r="H91" s="30"/>
       <c r="I91" s="81"/>
@@ -3367,28 +3428,101 @@
       <c r="N91" s="26"/>
     </row>
     <row r="92" spans="1:14" ht="11.25" customHeight="1">
-      <c r="A92" s="116"/>
-      <c r="B92" s="117"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="117"/>
-      <c r="E92" s="117"/>
-      <c r="F92" s="117"/>
-      <c r="G92" s="117"/>
-      <c r="H92" s="117"/>
-      <c r="I92" s="117"/>
-      <c r="J92" s="117"/>
-      <c r="K92" s="117"/>
-      <c r="L92" s="117"/>
-      <c r="M92" s="117"/>
-      <c r="N92" s="118"/>
+      <c r="A92" s="123"/>
+      <c r="B92" s="124"/>
+      <c r="C92" s="124"/>
+      <c r="D92" s="124"/>
+      <c r="E92" s="124"/>
+      <c r="F92" s="124"/>
+      <c r="G92" s="124"/>
+      <c r="H92" s="124"/>
+      <c r="I92" s="124"/>
+      <c r="J92" s="124"/>
+      <c r="K92" s="124"/>
+      <c r="L92" s="124"/>
+      <c r="M92" s="124"/>
+      <c r="N92" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A50:N50"/>
-    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A92:N92"/>
+    <mergeCell ref="A90:N90"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="A80:N80"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="A86:N86"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="A88:N88"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="A74:N74"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A78:N78"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="A70:N70"/>
+    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A64:N64"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="A58:N58"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="A52:N52"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A56:N56"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="I1:N7"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A12:N12"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A26:N26"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="A28:N28"/>
     <mergeCell ref="L9:L10"/>
@@ -3405,84 +3539,11 @@
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:G10"/>
     <mergeCell ref="A22:N22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="I1:N7"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A12:N12"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A52:N52"/>
-    <mergeCell ref="A54:N54"/>
-    <mergeCell ref="A56:N56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="A58:N58"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="A68:N68"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="A70:N70"/>
-    <mergeCell ref="A72:N72"/>
-    <mergeCell ref="A74:N74"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="A76:N76"/>
-    <mergeCell ref="A78:N78"/>
-    <mergeCell ref="A92:N92"/>
-    <mergeCell ref="A90:N90"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="A80:N80"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A84:N84"/>
-    <mergeCell ref="A86:N86"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="A88:N88"/>
-    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="D51:F51"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3515,98 +3576,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="142"/>
+      <c r="B1" s="140"/>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
     </row>
     <row r="2" spans="1:15" s="62" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
       <c r="E2" s="61"/>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
     </row>
     <row r="3" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="138"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
     </row>
     <row r="4" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="139" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="141"/>
+        <v>28</v>
+      </c>
+      <c r="B4" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="139"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
     </row>
     <row r="5" spans="1:15" s="70" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="139" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="141"/>
+        <v>30</v>
+      </c>
+      <c r="B5" s="137" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="139"/>
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
       <c r="O5" s="69"/>
     </row>
     <row r="6" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -3633,12 +3694,12 @@
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
       <c r="O6" s="66"/>
     </row>
     <row r="7" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -3657,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="111">
         <f>COUNTIF(A12:A200, "TC*")</f>
@@ -3665,128 +3726,128 @@
       </c>
       <c r="G7" s="72"/>
       <c r="H7" s="72"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
       <c r="O7" s="66"/>
     </row>
     <row r="8" spans="1:15" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="144"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
       <c r="E8" s="71"/>
       <c r="F8" s="71"/>
       <c r="G8" s="71"/>
       <c r="H8" s="71"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
-      <c r="L8" s="156"/>
-      <c r="M8" s="156"/>
-      <c r="N8" s="156"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
+      <c r="L8" s="158"/>
+      <c r="M8" s="158"/>
+      <c r="N8" s="158"/>
       <c r="O8" s="66"/>
     </row>
     <row r="9" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="145" t="s">
+      <c r="A9" s="129" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="145" t="s">
+      <c r="C9" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="D9" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145" t="s">
+      <c r="I9" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="145" t="s">
+      <c r="J9" s="129" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="145" t="s">
+      <c r="L9" s="129" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="130" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="145" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="152" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="145" t="s">
-        <v>40</v>
-      </c>
       <c r="O9" s="66"/>
     </row>
     <row r="10" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="145"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="152"/>
-      <c r="N10" s="145"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="129"/>
       <c r="O10" s="66"/>
     </row>
     <row r="11" spans="1:15" ht="15">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
       <c r="O11" s="74"/>
     </row>
     <row r="12" spans="1:15" s="76" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="157"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="157"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="157"/>
-      <c r="K12" s="157"/>
-      <c r="L12" s="157"/>
-      <c r="M12" s="157"/>
-      <c r="N12" s="157"/>
+      <c r="A12" s="159"/>
+      <c r="B12" s="159"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="159"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="159"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="159"/>
+      <c r="L12" s="159"/>
+      <c r="M12" s="159"/>
+      <c r="N12" s="159"/>
       <c r="O12" s="75"/>
     </row>
     <row r="13" spans="1:15" s="76" customFormat="1" ht="155.1" customHeight="1" outlineLevel="1">
       <c r="A13" s="15"/>
       <c r="B13" s="18"/>
       <c r="C13" s="31"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
       <c r="G13" s="19"/>
       <c r="H13" s="31"/>
       <c r="I13" s="20"/>
@@ -3800,9 +3861,9 @@
       <c r="A14" s="83"/>
       <c r="B14" s="83"/>
       <c r="C14" s="83"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="118"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
       <c r="G14" s="83"/>
       <c r="H14" s="83"/>
       <c r="I14" s="83"/>
@@ -3816,9 +3877,9 @@
       <c r="A15" s="15"/>
       <c r="B15" s="18"/>
       <c r="C15" s="31"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="20"/>
@@ -3832,9 +3893,9 @@
       <c r="A16" s="83"/>
       <c r="B16" s="83"/>
       <c r="C16" s="83"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
       <c r="G16" s="83"/>
       <c r="H16" s="83"/>
       <c r="I16" s="83"/>
@@ -3848,9 +3909,9 @@
       <c r="A17" s="15"/>
       <c r="B17" s="18"/>
       <c r="C17" s="31"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
       <c r="G17" s="19"/>
       <c r="H17" s="31"/>
       <c r="I17" s="20"/>
@@ -3864,9 +3925,9 @@
       <c r="A18" s="83"/>
       <c r="B18" s="83"/>
       <c r="C18" s="83"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="118"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="83"/>
       <c r="H18" s="83"/>
       <c r="I18" s="83"/>
@@ -3880,9 +3941,9 @@
       <c r="A19" s="15"/>
       <c r="B19" s="18"/>
       <c r="C19" s="31"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="151"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
       <c r="G19" s="19"/>
       <c r="H19" s="31"/>
       <c r="I19" s="20"/>
@@ -3896,9 +3957,9 @@
       <c r="A20" s="83"/>
       <c r="B20" s="83"/>
       <c r="C20" s="83"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="118"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="125"/>
       <c r="G20" s="83"/>
       <c r="H20" s="83"/>
       <c r="I20" s="83"/>
@@ -3912,9 +3973,9 @@
       <c r="A21" s="15"/>
       <c r="B21" s="18"/>
       <c r="C21" s="31"/>
-      <c r="D21" s="151"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="151"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
       <c r="G21" s="19"/>
       <c r="H21" s="31"/>
       <c r="I21" s="20"/>
@@ -3925,28 +3986,28 @@
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A22" s="153"/>
-      <c r="B22" s="153"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="153"/>
-      <c r="M22" s="153"/>
-      <c r="N22" s="153"/>
+      <c r="A22" s="157"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="157"/>
     </row>
     <row r="23" spans="1:14" ht="155.1" customHeight="1">
       <c r="A23" s="15"/>
       <c r="B23" s="18"/>
       <c r="C23" s="31"/>
-      <c r="D23" s="151"/>
-      <c r="E23" s="151"/>
-      <c r="F23" s="151"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
       <c r="G23" s="19"/>
       <c r="H23" s="31"/>
       <c r="I23" s="20"/>
@@ -3957,28 +4018,28 @@
       <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A24" s="153"/>
-      <c r="B24" s="153"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="153"/>
+      <c r="A24" s="157"/>
+      <c r="B24" s="157"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="157"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="157"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="157"/>
+      <c r="J24" s="157"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
     </row>
     <row r="25" spans="1:14" ht="155.1" customHeight="1">
       <c r="A25" s="15"/>
       <c r="B25" s="18"/>
       <c r="C25" s="31"/>
-      <c r="D25" s="151"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="20"/>
@@ -3989,28 +4050,28 @@
       <c r="N25" s="28"/>
     </row>
     <row r="26" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A26" s="153"/>
-      <c r="B26" s="153"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="153"/>
-      <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="153"/>
-      <c r="N26" s="153"/>
+      <c r="A26" s="157"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="157"/>
+      <c r="E26" s="157"/>
+      <c r="F26" s="157"/>
+      <c r="G26" s="157"/>
+      <c r="H26" s="157"/>
+      <c r="I26" s="157"/>
+      <c r="J26" s="157"/>
+      <c r="K26" s="157"/>
+      <c r="L26" s="157"/>
+      <c r="M26" s="157"/>
+      <c r="N26" s="157"/>
     </row>
     <row r="27" spans="1:14" ht="155.1" customHeight="1">
       <c r="A27" s="15"/>
       <c r="B27" s="18"/>
       <c r="C27" s="31"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
       <c r="G27" s="19"/>
       <c r="H27" s="31"/>
       <c r="I27" s="20"/>
@@ -4021,28 +4082,28 @@
       <c r="N27" s="28"/>
     </row>
     <row r="28" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A28" s="153"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
+      <c r="A28" s="157"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="157"/>
+      <c r="F28" s="157"/>
+      <c r="G28" s="157"/>
+      <c r="H28" s="157"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="157"/>
+      <c r="K28" s="157"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="157"/>
+      <c r="N28" s="157"/>
     </row>
     <row r="29" spans="1:14" ht="155.1" customHeight="1">
       <c r="A29" s="15"/>
       <c r="B29" s="18"/>
       <c r="C29" s="31"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
       <c r="G29" s="19"/>
       <c r="H29" s="31"/>
       <c r="I29" s="20"/>
@@ -4053,28 +4114,28 @@
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A30" s="153"/>
-      <c r="B30" s="153"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="153"/>
-      <c r="N30" s="153"/>
+      <c r="A30" s="157"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
     </row>
     <row r="31" spans="1:14" ht="155.1" customHeight="1">
       <c r="A31" s="15"/>
       <c r="B31" s="18"/>
       <c r="C31" s="31"/>
-      <c r="D31" s="151"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="151"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="132"/>
       <c r="G31" s="19"/>
       <c r="H31" s="31"/>
       <c r="I31" s="20"/>
@@ -4085,28 +4146,28 @@
       <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A32" s="153"/>
-      <c r="B32" s="153"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="153"/>
-      <c r="I32" s="153"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="153"/>
-      <c r="N32" s="153"/>
+      <c r="A32" s="157"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="157"/>
+      <c r="H32" s="157"/>
+      <c r="I32" s="157"/>
+      <c r="J32" s="157"/>
+      <c r="K32" s="157"/>
+      <c r="L32" s="157"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="157"/>
     </row>
     <row r="33" spans="1:14" ht="155.1" customHeight="1">
       <c r="A33" s="15"/>
       <c r="B33" s="18"/>
       <c r="C33" s="31"/>
-      <c r="D33" s="151"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
       <c r="G33" s="19"/>
       <c r="H33" s="21"/>
       <c r="I33" s="20"/>
@@ -4117,28 +4178,28 @@
       <c r="N33" s="26"/>
     </row>
     <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A34" s="153"/>
-      <c r="B34" s="153"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="153"/>
-      <c r="F34" s="153"/>
-      <c r="G34" s="153"/>
-      <c r="H34" s="153"/>
-      <c r="I34" s="153"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="153"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="153"/>
-      <c r="N34" s="153"/>
+      <c r="A34" s="157"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="157"/>
+      <c r="F34" s="157"/>
+      <c r="G34" s="157"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="157"/>
+      <c r="L34" s="157"/>
+      <c r="M34" s="157"/>
+      <c r="N34" s="157"/>
     </row>
     <row r="35" spans="1:14" ht="155.1" customHeight="1">
       <c r="A35" s="15"/>
       <c r="B35" s="18"/>
       <c r="C35" s="31"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
       <c r="G35" s="19"/>
       <c r="H35" s="21"/>
       <c r="I35" s="20"/>
@@ -4149,28 +4210,28 @@
       <c r="N35" s="26"/>
     </row>
     <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A36" s="153"/>
-      <c r="B36" s="153"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="153"/>
-      <c r="G36" s="153"/>
-      <c r="H36" s="153"/>
-      <c r="I36" s="153"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="153"/>
-      <c r="N36" s="153"/>
+      <c r="A36" s="157"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="157"/>
+      <c r="D36" s="157"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="157"/>
+      <c r="H36" s="157"/>
+      <c r="I36" s="157"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="157"/>
+      <c r="L36" s="157"/>
+      <c r="M36" s="157"/>
+      <c r="N36" s="157"/>
     </row>
     <row r="37" spans="1:14" ht="155.1" customHeight="1">
       <c r="A37" s="15"/>
       <c r="B37" s="18"/>
       <c r="C37" s="31"/>
-      <c r="D37" s="151"/>
-      <c r="E37" s="151"/>
-      <c r="F37" s="151"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
       <c r="G37" s="19"/>
       <c r="H37" s="21"/>
       <c r="I37" s="20"/>
@@ -4181,28 +4242,28 @@
       <c r="N37" s="26"/>
     </row>
     <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A38" s="153"/>
-      <c r="B38" s="153"/>
-      <c r="C38" s="153"/>
-      <c r="D38" s="153"/>
-      <c r="E38" s="153"/>
-      <c r="F38" s="153"/>
-      <c r="G38" s="153"/>
-      <c r="H38" s="153"/>
-      <c r="I38" s="153"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="153"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="153"/>
-      <c r="N38" s="153"/>
+      <c r="A38" s="157"/>
+      <c r="B38" s="157"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="157"/>
+      <c r="E38" s="157"/>
+      <c r="F38" s="157"/>
+      <c r="G38" s="157"/>
+      <c r="H38" s="157"/>
+      <c r="I38" s="157"/>
+      <c r="J38" s="157"/>
+      <c r="K38" s="157"/>
+      <c r="L38" s="157"/>
+      <c r="M38" s="157"/>
+      <c r="N38" s="157"/>
     </row>
     <row r="39" spans="1:14" ht="155.1" customHeight="1">
       <c r="A39" s="15"/>
       <c r="B39" s="18"/>
       <c r="C39" s="31"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
       <c r="G39" s="19"/>
       <c r="H39" s="21"/>
       <c r="I39" s="20"/>
@@ -4213,28 +4274,28 @@
       <c r="N39" s="42"/>
     </row>
     <row r="40" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A40" s="153"/>
-      <c r="B40" s="153"/>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="153"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="153"/>
-      <c r="K40" s="153"/>
-      <c r="L40" s="153"/>
-      <c r="M40" s="153"/>
-      <c r="N40" s="153"/>
+      <c r="A40" s="157"/>
+      <c r="B40" s="157"/>
+      <c r="C40" s="157"/>
+      <c r="D40" s="157"/>
+      <c r="E40" s="157"/>
+      <c r="F40" s="157"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="157"/>
+      <c r="I40" s="157"/>
+      <c r="J40" s="157"/>
+      <c r="K40" s="157"/>
+      <c r="L40" s="157"/>
+      <c r="M40" s="157"/>
+      <c r="N40" s="157"/>
     </row>
     <row r="41" spans="1:14" ht="155.1" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="18"/>
       <c r="C41" s="31"/>
-      <c r="D41" s="151"/>
-      <c r="E41" s="151"/>
-      <c r="F41" s="151"/>
+      <c r="D41" s="132"/>
+      <c r="E41" s="132"/>
+      <c r="F41" s="132"/>
       <c r="G41" s="19"/>
       <c r="H41" s="21"/>
       <c r="I41" s="20"/>
@@ -4245,20 +4306,20 @@
       <c r="N41" s="42"/>
     </row>
     <row r="42" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A42" s="147"/>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="147"/>
+      <c r="A42" s="144"/>
+      <c r="B42" s="144"/>
+      <c r="C42" s="144"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="144"/>
+      <c r="F42" s="144"/>
+      <c r="G42" s="144"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="144"/>
+      <c r="J42" s="144"/>
+      <c r="K42" s="144"/>
+      <c r="L42" s="144"/>
+      <c r="M42" s="144"/>
+      <c r="N42" s="144"/>
     </row>
     <row r="43" spans="1:14" ht="140.1" customHeight="1">
       <c r="A43" s="15"/>
@@ -4277,20 +4338,20 @@
       <c r="N43" s="28"/>
     </row>
     <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A44" s="153"/>
-      <c r="B44" s="153"/>
-      <c r="C44" s="153"/>
-      <c r="D44" s="153"/>
-      <c r="E44" s="153"/>
-      <c r="F44" s="153"/>
-      <c r="G44" s="153"/>
-      <c r="H44" s="153"/>
-      <c r="I44" s="153"/>
-      <c r="J44" s="153"/>
-      <c r="K44" s="153"/>
-      <c r="L44" s="153"/>
-      <c r="M44" s="153"/>
-      <c r="N44" s="153"/>
+      <c r="A44" s="157"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="157"/>
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="157"/>
+      <c r="K44" s="157"/>
+      <c r="L44" s="157"/>
+      <c r="M44" s="157"/>
+      <c r="N44" s="157"/>
     </row>
     <row r="45" spans="1:14" ht="168.75" customHeight="1">
       <c r="A45" s="15"/>
@@ -4309,20 +4370,20 @@
       <c r="N45" s="26"/>
     </row>
     <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A46" s="153"/>
-      <c r="B46" s="153"/>
-      <c r="C46" s="153"/>
-      <c r="D46" s="153"/>
-      <c r="E46" s="153"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="153"/>
-      <c r="H46" s="153"/>
-      <c r="I46" s="153"/>
-      <c r="J46" s="153"/>
-      <c r="K46" s="153"/>
-      <c r="L46" s="153"/>
-      <c r="M46" s="153"/>
-      <c r="N46" s="153"/>
+      <c r="A46" s="157"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="157"/>
+      <c r="D46" s="157"/>
+      <c r="E46" s="157"/>
+      <c r="F46" s="157"/>
+      <c r="G46" s="157"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="157"/>
+      <c r="K46" s="157"/>
+      <c r="L46" s="157"/>
+      <c r="M46" s="157"/>
+      <c r="N46" s="157"/>
     </row>
     <row r="47" spans="1:14" ht="154.5" customHeight="1">
       <c r="A47" s="15"/>
@@ -4341,20 +4402,20 @@
       <c r="N47" s="26"/>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A48" s="153"/>
-      <c r="B48" s="153"/>
-      <c r="C48" s="153"/>
-      <c r="D48" s="153"/>
-      <c r="E48" s="153"/>
-      <c r="F48" s="153"/>
-      <c r="G48" s="153"/>
-      <c r="H48" s="153"/>
-      <c r="I48" s="153"/>
-      <c r="J48" s="153"/>
-      <c r="K48" s="153"/>
-      <c r="L48" s="153"/>
-      <c r="M48" s="153"/>
-      <c r="N48" s="153"/>
+      <c r="A48" s="157"/>
+      <c r="B48" s="157"/>
+      <c r="C48" s="157"/>
+      <c r="D48" s="157"/>
+      <c r="E48" s="157"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="157"/>
+      <c r="H48" s="157"/>
+      <c r="I48" s="157"/>
+      <c r="J48" s="157"/>
+      <c r="K48" s="157"/>
+      <c r="L48" s="157"/>
+      <c r="M48" s="157"/>
+      <c r="N48" s="157"/>
     </row>
     <row r="49" spans="1:14" ht="158.25" customHeight="1">
       <c r="A49" s="15"/>
@@ -4373,20 +4434,20 @@
       <c r="N49" s="28"/>
     </row>
     <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A50" s="153"/>
-      <c r="B50" s="153"/>
-      <c r="C50" s="153"/>
-      <c r="D50" s="153"/>
-      <c r="E50" s="153"/>
-      <c r="F50" s="153"/>
-      <c r="G50" s="153"/>
-      <c r="H50" s="153"/>
-      <c r="I50" s="153"/>
-      <c r="J50" s="153"/>
-      <c r="K50" s="153"/>
-      <c r="L50" s="153"/>
-      <c r="M50" s="153"/>
-      <c r="N50" s="153"/>
+      <c r="A50" s="157"/>
+      <c r="B50" s="157"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="157"/>
+      <c r="E50" s="157"/>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="157"/>
+      <c r="J50" s="157"/>
+      <c r="K50" s="157"/>
+      <c r="L50" s="157"/>
+      <c r="M50" s="157"/>
+      <c r="N50" s="157"/>
     </row>
     <row r="51" spans="1:14" ht="157.5" customHeight="1">
       <c r="A51" s="15"/>
@@ -4405,20 +4466,20 @@
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A52" s="153"/>
-      <c r="B52" s="153"/>
-      <c r="C52" s="153"/>
-      <c r="D52" s="153"/>
-      <c r="E52" s="153"/>
-      <c r="F52" s="153"/>
-      <c r="G52" s="153"/>
-      <c r="H52" s="153"/>
-      <c r="I52" s="153"/>
-      <c r="J52" s="153"/>
-      <c r="K52" s="153"/>
-      <c r="L52" s="153"/>
-      <c r="M52" s="153"/>
-      <c r="N52" s="153"/>
+      <c r="A52" s="157"/>
+      <c r="B52" s="157"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="157"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="157"/>
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="157"/>
+      <c r="K52" s="157"/>
+      <c r="L52" s="157"/>
+      <c r="M52" s="157"/>
+      <c r="N52" s="157"/>
     </row>
     <row r="53" spans="1:14" ht="162.75" customHeight="1">
       <c r="A53" s="15"/>
@@ -4437,20 +4498,20 @@
       <c r="N53" s="28"/>
     </row>
     <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A54" s="153"/>
-      <c r="B54" s="153"/>
-      <c r="C54" s="153"/>
-      <c r="D54" s="153"/>
-      <c r="E54" s="153"/>
-      <c r="F54" s="153"/>
-      <c r="G54" s="153"/>
-      <c r="H54" s="153"/>
-      <c r="I54" s="153"/>
-      <c r="J54" s="153"/>
-      <c r="K54" s="153"/>
-      <c r="L54" s="153"/>
-      <c r="M54" s="153"/>
-      <c r="N54" s="153"/>
+      <c r="A54" s="157"/>
+      <c r="B54" s="157"/>
+      <c r="C54" s="157"/>
+      <c r="D54" s="157"/>
+      <c r="E54" s="157"/>
+      <c r="F54" s="157"/>
+      <c r="G54" s="157"/>
+      <c r="H54" s="157"/>
+      <c r="I54" s="157"/>
+      <c r="J54" s="157"/>
+      <c r="K54" s="157"/>
+      <c r="L54" s="157"/>
+      <c r="M54" s="157"/>
+      <c r="N54" s="157"/>
     </row>
     <row r="55" spans="1:14" ht="149.25" customHeight="1">
       <c r="A55" s="15"/>
@@ -4469,20 +4530,20 @@
       <c r="N55" s="26"/>
     </row>
     <row r="56" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A56" s="153"/>
-      <c r="B56" s="153"/>
-      <c r="C56" s="153"/>
-      <c r="D56" s="153"/>
-      <c r="E56" s="153"/>
-      <c r="F56" s="153"/>
-      <c r="G56" s="153"/>
-      <c r="H56" s="153"/>
-      <c r="I56" s="153"/>
-      <c r="J56" s="153"/>
-      <c r="K56" s="153"/>
-      <c r="L56" s="153"/>
-      <c r="M56" s="153"/>
-      <c r="N56" s="153"/>
+      <c r="A56" s="157"/>
+      <c r="B56" s="157"/>
+      <c r="C56" s="157"/>
+      <c r="D56" s="157"/>
+      <c r="E56" s="157"/>
+      <c r="F56" s="157"/>
+      <c r="G56" s="157"/>
+      <c r="H56" s="157"/>
+      <c r="I56" s="157"/>
+      <c r="J56" s="157"/>
+      <c r="K56" s="157"/>
+      <c r="L56" s="157"/>
+      <c r="M56" s="157"/>
+      <c r="N56" s="157"/>
     </row>
     <row r="57" spans="1:14" ht="158.25" customHeight="1">
       <c r="A57" s="15"/>
@@ -4500,20 +4561,20 @@
       <c r="N57" s="42"/>
     </row>
     <row r="58" spans="1:14" ht="21" customHeight="1">
-      <c r="A58" s="147"/>
-      <c r="B58" s="147"/>
-      <c r="C58" s="147"/>
-      <c r="D58" s="147"/>
-      <c r="E58" s="147"/>
-      <c r="F58" s="147"/>
-      <c r="G58" s="147"/>
-      <c r="H58" s="147"/>
-      <c r="I58" s="147"/>
-      <c r="J58" s="147"/>
-      <c r="K58" s="147"/>
-      <c r="L58" s="147"/>
-      <c r="M58" s="147"/>
-      <c r="N58" s="147"/>
+      <c r="A58" s="144"/>
+      <c r="B58" s="144"/>
+      <c r="C58" s="144"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="144"/>
+      <c r="J58" s="144"/>
+      <c r="K58" s="144"/>
+      <c r="L58" s="144"/>
+      <c r="M58" s="144"/>
+      <c r="N58" s="144"/>
     </row>
     <row r="59" spans="1:14" ht="140.1" customHeight="1">
       <c r="A59" s="15"/>
@@ -4532,20 +4593,20 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A60" s="153"/>
-      <c r="B60" s="153"/>
-      <c r="C60" s="153"/>
-      <c r="D60" s="153"/>
-      <c r="E60" s="153"/>
-      <c r="F60" s="153"/>
-      <c r="G60" s="153"/>
-      <c r="H60" s="153"/>
-      <c r="I60" s="153"/>
-      <c r="J60" s="153"/>
-      <c r="K60" s="153"/>
-      <c r="L60" s="153"/>
-      <c r="M60" s="153"/>
-      <c r="N60" s="153"/>
+      <c r="A60" s="157"/>
+      <c r="B60" s="157"/>
+      <c r="C60" s="157"/>
+      <c r="D60" s="157"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="157"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="157"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="157"/>
+      <c r="L60" s="157"/>
+      <c r="M60" s="157"/>
+      <c r="N60" s="157"/>
     </row>
     <row r="61" spans="1:14" ht="140.1" customHeight="1">
       <c r="A61" s="15"/>
@@ -4564,20 +4625,20 @@
       <c r="N61" s="26"/>
     </row>
     <row r="62" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A62" s="153"/>
-      <c r="B62" s="153"/>
-      <c r="C62" s="153"/>
-      <c r="D62" s="153"/>
-      <c r="E62" s="153"/>
-      <c r="F62" s="153"/>
-      <c r="G62" s="153"/>
-      <c r="H62" s="153"/>
-      <c r="I62" s="153"/>
-      <c r="J62" s="153"/>
-      <c r="K62" s="153"/>
-      <c r="L62" s="153"/>
-      <c r="M62" s="153"/>
-      <c r="N62" s="153"/>
+      <c r="A62" s="157"/>
+      <c r="B62" s="157"/>
+      <c r="C62" s="157"/>
+      <c r="D62" s="157"/>
+      <c r="E62" s="157"/>
+      <c r="F62" s="157"/>
+      <c r="G62" s="157"/>
+      <c r="H62" s="157"/>
+      <c r="I62" s="157"/>
+      <c r="J62" s="157"/>
+      <c r="K62" s="157"/>
+      <c r="L62" s="157"/>
+      <c r="M62" s="157"/>
+      <c r="N62" s="157"/>
     </row>
     <row r="63" spans="1:14" ht="140.1" customHeight="1">
       <c r="A63" s="15"/>
@@ -4596,20 +4657,20 @@
       <c r="N63" s="28"/>
     </row>
     <row r="64" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A64" s="154"/>
-      <c r="B64" s="154"/>
-      <c r="C64" s="154"/>
-      <c r="D64" s="154"/>
-      <c r="E64" s="154"/>
-      <c r="F64" s="154"/>
-      <c r="G64" s="154"/>
-      <c r="H64" s="154"/>
-      <c r="I64" s="154"/>
-      <c r="J64" s="154"/>
-      <c r="K64" s="154"/>
-      <c r="L64" s="154"/>
-      <c r="M64" s="154"/>
-      <c r="N64" s="154"/>
+      <c r="A64" s="161"/>
+      <c r="B64" s="161"/>
+      <c r="C64" s="161"/>
+      <c r="D64" s="161"/>
+      <c r="E64" s="161"/>
+      <c r="F64" s="161"/>
+      <c r="G64" s="161"/>
+      <c r="H64" s="161"/>
+      <c r="I64" s="161"/>
+      <c r="J64" s="161"/>
+      <c r="K64" s="161"/>
+      <c r="L64" s="161"/>
+      <c r="M64" s="161"/>
+      <c r="N64" s="161"/>
     </row>
     <row r="65" spans="1:14" ht="140.1" customHeight="1">
       <c r="A65" s="15"/>
@@ -4628,20 +4689,20 @@
       <c r="N65" s="26"/>
     </row>
     <row r="66" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A66" s="147"/>
-      <c r="B66" s="147"/>
-      <c r="C66" s="147"/>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="147"/>
-      <c r="H66" s="147"/>
-      <c r="I66" s="147"/>
-      <c r="J66" s="147"/>
-      <c r="K66" s="147"/>
-      <c r="L66" s="147"/>
-      <c r="M66" s="147"/>
-      <c r="N66" s="147"/>
+      <c r="A66" s="144"/>
+      <c r="B66" s="144"/>
+      <c r="C66" s="144"/>
+      <c r="D66" s="144"/>
+      <c r="E66" s="144"/>
+      <c r="F66" s="144"/>
+      <c r="G66" s="144"/>
+      <c r="H66" s="144"/>
+      <c r="I66" s="144"/>
+      <c r="J66" s="144"/>
+      <c r="K66" s="144"/>
+      <c r="L66" s="144"/>
+      <c r="M66" s="144"/>
+      <c r="N66" s="144"/>
     </row>
     <row r="67" spans="1:14" ht="140.1" customHeight="1">
       <c r="A67" s="15"/>
@@ -4660,20 +4721,20 @@
       <c r="N67" s="28"/>
     </row>
     <row r="68" spans="1:14" ht="11.25" customHeight="1">
-      <c r="A68" s="155"/>
-      <c r="B68" s="155"/>
-      <c r="C68" s="155"/>
-      <c r="D68" s="155"/>
-      <c r="E68" s="155"/>
-      <c r="F68" s="155"/>
-      <c r="G68" s="155"/>
-      <c r="H68" s="155"/>
-      <c r="I68" s="155"/>
-      <c r="J68" s="155"/>
-      <c r="K68" s="155"/>
-      <c r="L68" s="155"/>
-      <c r="M68" s="155"/>
-      <c r="N68" s="155"/>
+      <c r="A68" s="160"/>
+      <c r="B68" s="160"/>
+      <c r="C68" s="160"/>
+      <c r="D68" s="160"/>
+      <c r="E68" s="160"/>
+      <c r="F68" s="160"/>
+      <c r="G68" s="160"/>
+      <c r="H68" s="160"/>
+      <c r="I68" s="160"/>
+      <c r="J68" s="160"/>
+      <c r="K68" s="160"/>
+      <c r="L68" s="160"/>
+      <c r="M68" s="160"/>
+      <c r="N68" s="160"/>
     </row>
     <row r="69" spans="1:14" ht="142.5" customHeight="1">
       <c r="A69" s="15"/>
@@ -4692,20 +4753,20 @@
       <c r="N69" s="28"/>
     </row>
     <row r="70" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A70" s="153"/>
-      <c r="B70" s="153"/>
-      <c r="C70" s="153"/>
-      <c r="D70" s="153"/>
-      <c r="E70" s="153"/>
-      <c r="F70" s="153"/>
-      <c r="G70" s="153"/>
-      <c r="H70" s="153"/>
-      <c r="I70" s="153"/>
-      <c r="J70" s="153"/>
-      <c r="K70" s="153"/>
-      <c r="L70" s="153"/>
-      <c r="M70" s="153"/>
-      <c r="N70" s="153"/>
+      <c r="A70" s="157"/>
+      <c r="B70" s="157"/>
+      <c r="C70" s="157"/>
+      <c r="D70" s="157"/>
+      <c r="E70" s="157"/>
+      <c r="F70" s="157"/>
+      <c r="G70" s="157"/>
+      <c r="H70" s="157"/>
+      <c r="I70" s="157"/>
+      <c r="J70" s="157"/>
+      <c r="K70" s="157"/>
+      <c r="L70" s="157"/>
+      <c r="M70" s="157"/>
+      <c r="N70" s="157"/>
     </row>
     <row r="71" spans="1:14" ht="140.1" customHeight="1">
       <c r="A71" s="15"/>
@@ -4724,20 +4785,20 @@
       <c r="N71" s="28"/>
     </row>
     <row r="72" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A72" s="153"/>
-      <c r="B72" s="153"/>
-      <c r="C72" s="153"/>
-      <c r="D72" s="153"/>
-      <c r="E72" s="153"/>
-      <c r="F72" s="153"/>
-      <c r="G72" s="153"/>
-      <c r="H72" s="153"/>
-      <c r="I72" s="153"/>
-      <c r="J72" s="153"/>
-      <c r="K72" s="153"/>
-      <c r="L72" s="153"/>
-      <c r="M72" s="153"/>
-      <c r="N72" s="153"/>
+      <c r="A72" s="157"/>
+      <c r="B72" s="157"/>
+      <c r="C72" s="157"/>
+      <c r="D72" s="157"/>
+      <c r="E72" s="157"/>
+      <c r="F72" s="157"/>
+      <c r="G72" s="157"/>
+      <c r="H72" s="157"/>
+      <c r="I72" s="157"/>
+      <c r="J72" s="157"/>
+      <c r="K72" s="157"/>
+      <c r="L72" s="157"/>
+      <c r="M72" s="157"/>
+      <c r="N72" s="157"/>
     </row>
     <row r="73" spans="1:14" ht="140.1" customHeight="1">
       <c r="A73" s="15"/>
@@ -4756,20 +4817,20 @@
       <c r="N73" s="28"/>
     </row>
     <row r="74" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A74" s="153"/>
-      <c r="B74" s="153"/>
-      <c r="C74" s="153"/>
-      <c r="D74" s="153"/>
-      <c r="E74" s="153"/>
-      <c r="F74" s="153"/>
-      <c r="G74" s="153"/>
-      <c r="H74" s="153"/>
-      <c r="I74" s="153"/>
-      <c r="J74" s="153"/>
-      <c r="K74" s="153"/>
-      <c r="L74" s="153"/>
-      <c r="M74" s="153"/>
-      <c r="N74" s="153"/>
+      <c r="A74" s="157"/>
+      <c r="B74" s="157"/>
+      <c r="C74" s="157"/>
+      <c r="D74" s="157"/>
+      <c r="E74" s="157"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="157"/>
+      <c r="H74" s="157"/>
+      <c r="I74" s="157"/>
+      <c r="J74" s="157"/>
+      <c r="K74" s="157"/>
+      <c r="L74" s="157"/>
+      <c r="M74" s="157"/>
+      <c r="N74" s="157"/>
     </row>
     <row r="75" spans="1:14" ht="140.1" customHeight="1">
       <c r="A75" s="15"/>
@@ -4788,28 +4849,28 @@
       <c r="N75" s="28"/>
     </row>
     <row r="76" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A76" s="116"/>
-      <c r="B76" s="117"/>
-      <c r="C76" s="117"/>
-      <c r="D76" s="117"/>
-      <c r="E76" s="117"/>
-      <c r="F76" s="117"/>
-      <c r="G76" s="117"/>
-      <c r="H76" s="117"/>
-      <c r="I76" s="117"/>
-      <c r="J76" s="117"/>
-      <c r="K76" s="117"/>
-      <c r="L76" s="117"/>
-      <c r="M76" s="117"/>
-      <c r="N76" s="118"/>
+      <c r="A76" s="123"/>
+      <c r="B76" s="124"/>
+      <c r="C76" s="124"/>
+      <c r="D76" s="124"/>
+      <c r="E76" s="124"/>
+      <c r="F76" s="124"/>
+      <c r="G76" s="124"/>
+      <c r="H76" s="124"/>
+      <c r="I76" s="124"/>
+      <c r="J76" s="124"/>
+      <c r="K76" s="124"/>
+      <c r="L76" s="124"/>
+      <c r="M76" s="124"/>
+      <c r="N76" s="125"/>
     </row>
     <row r="77" spans="1:14" ht="140.1" customHeight="1">
       <c r="A77" s="15"/>
       <c r="B77" s="18"/>
       <c r="C77" s="31"/>
-      <c r="D77" s="128"/>
-      <c r="E77" s="129"/>
-      <c r="F77" s="130"/>
+      <c r="D77" s="154"/>
+      <c r="E77" s="155"/>
+      <c r="F77" s="156"/>
       <c r="G77" s="19"/>
       <c r="H77" s="18"/>
       <c r="I77" s="20"/>
@@ -4820,20 +4881,20 @@
       <c r="N77" s="28"/>
     </row>
     <row r="78" spans="1:14" ht="9.9499999999999993" customHeight="1">
-      <c r="A78" s="116"/>
-      <c r="B78" s="117"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="117"/>
-      <c r="E78" s="117"/>
-      <c r="F78" s="117"/>
-      <c r="G78" s="117"/>
-      <c r="H78" s="117"/>
-      <c r="I78" s="117"/>
-      <c r="J78" s="117"/>
-      <c r="K78" s="117"/>
-      <c r="L78" s="117"/>
-      <c r="M78" s="117"/>
-      <c r="N78" s="118"/>
+      <c r="A78" s="123"/>
+      <c r="B78" s="124"/>
+      <c r="C78" s="124"/>
+      <c r="D78" s="124"/>
+      <c r="E78" s="124"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="124"/>
+      <c r="H78" s="124"/>
+      <c r="I78" s="124"/>
+      <c r="J78" s="124"/>
+      <c r="K78" s="124"/>
+      <c r="L78" s="124"/>
+      <c r="M78" s="124"/>
+      <c r="N78" s="125"/>
     </row>
     <row r="79" spans="1:14" ht="140.1" customHeight="1"/>
     <row r="80" spans="1:14" ht="9.9499999999999993" customHeight="1"/>
@@ -4888,19 +4949,62 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="A52:N52"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A56:N56"/>
+    <mergeCell ref="A58:N58"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="A74:N74"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A64:N64"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A78:N78"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="A70:N70"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="D71:F71"/>
     <mergeCell ref="I1:N8"/>
     <mergeCell ref="A11:N11"/>
     <mergeCell ref="A12:N12"/>
@@ -4917,62 +5021,19 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A78:N78"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="A68:N68"/>
-    <mergeCell ref="A70:N70"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="A76:N76"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="A72:N72"/>
-    <mergeCell ref="A74:N74"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="A56:N56"/>
-    <mergeCell ref="A58:N58"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A52:N52"/>
-    <mergeCell ref="A54:N54"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A50:N50"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5002,98 +5063,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="142"/>
+      <c r="B1" s="140"/>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
     </row>
     <row r="2" spans="1:15" s="62" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
       <c r="E2" s="61"/>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
     </row>
     <row r="3" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="138"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
     </row>
     <row r="4" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="139" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="141"/>
+        <v>28</v>
+      </c>
+      <c r="B4" s="137" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="139"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
     </row>
     <row r="5" spans="1:15" s="70" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="139" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="141"/>
+        <v>30</v>
+      </c>
+      <c r="B5" s="137" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="139"/>
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
       <c r="O5" s="69"/>
     </row>
     <row r="6" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -5120,12 +5181,12 @@
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
       <c r="O6" s="66"/>
     </row>
     <row r="7" spans="1:15" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -5144,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="111">
         <f>COUNTIF(A12:A200, "TC*")</f>
@@ -5152,119 +5213,119 @@
       </c>
       <c r="G7" s="72"/>
       <c r="H7" s="72"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
       <c r="O7" s="66"/>
     </row>
     <row r="8" spans="1:15" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="144"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
       <c r="E8" s="71"/>
       <c r="F8" s="71"/>
       <c r="G8" s="71"/>
       <c r="H8" s="71"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
-      <c r="L8" s="156"/>
-      <c r="M8" s="156"/>
-      <c r="N8" s="156"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
+      <c r="L8" s="158"/>
+      <c r="M8" s="158"/>
+      <c r="N8" s="158"/>
       <c r="O8" s="66"/>
     </row>
     <row r="9" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="145" t="s">
+      <c r="A9" s="129" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="145" t="s">
+      <c r="C9" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="D9" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145" t="s">
+      <c r="I9" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="145" t="s">
+      <c r="J9" s="129" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="145" t="s">
+      <c r="L9" s="129" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="130" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="145" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="152" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="145" t="s">
-        <v>40</v>
-      </c>
       <c r="O9" s="66"/>
     </row>
     <row r="10" spans="1:15" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="145"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="152"/>
-      <c r="N10" s="145"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="129"/>
       <c r="O10" s="66"/>
     </row>
     <row r="11" spans="1:15" ht="15">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
       <c r="O11" s="74"/>
     </row>
     <row r="12" spans="1:15" s="76" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="147"/>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="144"/>
+      <c r="C12" s="144"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
       <c r="O12" s="75"/>
     </row>
     <row r="13" spans="1:15" s="76" customFormat="1" ht="140.1" customHeight="1" outlineLevel="1">
@@ -5287,9 +5348,9 @@
       <c r="A14" s="83"/>
       <c r="B14" s="83"/>
       <c r="C14" s="83"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="118"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
       <c r="G14" s="83"/>
       <c r="H14" s="83"/>
       <c r="I14" s="83"/>
@@ -5319,9 +5380,9 @@
       <c r="A16" s="83"/>
       <c r="B16" s="83"/>
       <c r="C16" s="83"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
       <c r="G16" s="83"/>
       <c r="H16" s="83"/>
       <c r="I16" s="83"/>
@@ -5348,20 +5409,20 @@
       <c r="N17" s="23"/>
     </row>
     <row r="18" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A18" s="147"/>
-      <c r="B18" s="147"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="147"/>
-      <c r="M18" s="147"/>
-      <c r="N18" s="147"/>
+      <c r="A18" s="144"/>
+      <c r="B18" s="144"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="144"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="144"/>
+      <c r="J18" s="144"/>
+      <c r="K18" s="144"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
     </row>
     <row r="19" spans="1:14" ht="140.1" customHeight="1">
       <c r="A19" s="15"/>
@@ -5383,9 +5444,9 @@
       <c r="A20" s="83"/>
       <c r="B20" s="83"/>
       <c r="C20" s="83"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="118"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="125"/>
       <c r="G20" s="83"/>
       <c r="H20" s="83"/>
       <c r="I20" s="83"/>
@@ -5412,20 +5473,20 @@
       <c r="N21" s="42"/>
     </row>
     <row r="22" spans="1:14" ht="12" customHeight="1">
-      <c r="A22" s="153"/>
-      <c r="B22" s="153"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="153"/>
-      <c r="M22" s="153"/>
-      <c r="N22" s="153"/>
+      <c r="A22" s="157"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="157"/>
     </row>
     <row r="23" spans="1:14" ht="140.1" customHeight="1">
       <c r="A23" s="15"/>
@@ -5444,20 +5505,20 @@
       <c r="N23" s="42"/>
     </row>
     <row r="24" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A24" s="147"/>
-      <c r="B24" s="147"/>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="147"/>
-      <c r="G24" s="147"/>
-      <c r="H24" s="147"/>
-      <c r="I24" s="147"/>
-      <c r="J24" s="147"/>
-      <c r="K24" s="147"/>
-      <c r="L24" s="147"/>
-      <c r="M24" s="147"/>
-      <c r="N24" s="147"/>
+      <c r="A24" s="144"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="144"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="144"/>
+      <c r="N24" s="144"/>
     </row>
     <row r="25" spans="1:14" ht="140.1" customHeight="1">
       <c r="A25" s="15"/>
@@ -5476,20 +5537,20 @@
       <c r="N25" s="28"/>
     </row>
     <row r="26" spans="1:14" ht="12" customHeight="1">
-      <c r="A26" s="153"/>
-      <c r="B26" s="153"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="153"/>
-      <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="153"/>
-      <c r="N26" s="153"/>
+      <c r="A26" s="157"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="157"/>
+      <c r="E26" s="157"/>
+      <c r="F26" s="157"/>
+      <c r="G26" s="157"/>
+      <c r="H26" s="157"/>
+      <c r="I26" s="157"/>
+      <c r="J26" s="157"/>
+      <c r="K26" s="157"/>
+      <c r="L26" s="157"/>
+      <c r="M26" s="157"/>
+      <c r="N26" s="157"/>
     </row>
     <row r="27" spans="1:14" ht="140.1" customHeight="1">
       <c r="A27" s="15"/>
@@ -5508,20 +5569,20 @@
       <c r="N27" s="28"/>
     </row>
     <row r="28" spans="1:14" ht="12" customHeight="1">
-      <c r="A28" s="153"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
+      <c r="A28" s="157"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="157"/>
+      <c r="F28" s="157"/>
+      <c r="G28" s="157"/>
+      <c r="H28" s="157"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="157"/>
+      <c r="K28" s="157"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="157"/>
+      <c r="N28" s="157"/>
     </row>
     <row r="29" spans="1:14" ht="140.1" customHeight="1">
       <c r="A29" s="15"/>
@@ -5540,20 +5601,20 @@
       <c r="N29" s="42"/>
     </row>
     <row r="30" spans="1:14" ht="12" customHeight="1">
-      <c r="A30" s="153"/>
-      <c r="B30" s="153"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="153"/>
-      <c r="N30" s="153"/>
+      <c r="A30" s="157"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
     </row>
     <row r="31" spans="1:14" ht="140.1" customHeight="1">
       <c r="A31" s="15"/>
@@ -5796,24 +5857,10 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="I1:N8"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A28:N28"/>
     <mergeCell ref="A30:N30"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D23:F23"/>
@@ -5830,10 +5877,24 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="A22:N22"/>
     <mergeCell ref="A24:N24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="I1:N8"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A8:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5871,7 +5932,7 @@
     <row r="2" spans="1:11" ht="21" thickBot="1">
       <c r="A2" s="35"/>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
@@ -5881,10 +5942,10 @@
     </row>
     <row r="3" spans="1:11" ht="15.95" customHeight="1">
       <c r="B3" s="55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -5893,15 +5954,15 @@
     </row>
     <row r="4" spans="1:11" ht="15.95" customHeight="1">
       <c r="B4" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="160">
+        <v>42</v>
+      </c>
+      <c r="C4" s="113">
         <v>46221</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.95" customHeight="1">
       <c r="B5" s="85" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="86">
         <f>COUNTIF('Test User Module'!$N$1:$N$200, "*Fail*") + COUNTIF('Test User Module'!$N$1:$N$200, "*Fail*") + COUNTIF('System Test '!$N$1:$N$200, "*Fail*")</f>
@@ -5910,7 +5971,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.95" customHeight="1" thickBot="1">
       <c r="B6" s="58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="60"/>
     </row>
@@ -5920,10 +5981,10 @@
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1">
       <c r="B9" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>2</v>
@@ -5944,10 +6005,10 @@
         <v>8</v>
       </c>
       <c r="J9" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="41" t="s">
         <v>46</v>
-      </c>
-      <c r="K9" s="41" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1">
@@ -5960,7 +6021,7 @@
       </c>
       <c r="D10" s="43">
         <f>'Test User Module'!$B$6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="28">
         <f>'Test User Module'!B7</f>
@@ -5972,7 +6033,7 @@
       </c>
       <c r="G10" s="43">
         <f>'Test User Module'!$D$6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="43">
         <f>'Test User Module'!$D$7</f>
@@ -6076,11 +6137,11 @@
     <row r="13" spans="1:11" ht="18" customHeight="1" thickBot="1">
       <c r="B13" s="46"/>
       <c r="C13" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="47">
         <f t="shared" ref="D13:K13" si="0">SUM(D6:D12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="47">
         <f t="shared" si="0"/>
@@ -6092,7 +6153,7 @@
       </c>
       <c r="G13" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="47">
         <f t="shared" si="0"/>
@@ -6115,10 +6176,10 @@
     <row r="15" spans="1:11" ht="18" customHeight="1" thickBot="1"/>
     <row r="16" spans="1:11" ht="18" customHeight="1">
       <c r="B16" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>10</v>
